--- a/olympic-new-compare-audit.xlsx
+++ b/olympic-new-compare-audit.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="901">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">OL186GFETLCFK</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC KILN 186GFETLC FURNITURE KIT 2 full shelves, 3 : 1/2" posts 3 </t>
+    <t xml:space="preserve">Olympic Kilns 186Gfetlc Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">146.00</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">OLBFEC</t>
   </si>
   <si>
-    <t xml:space="preserve">Electronic controller - Bo&amp;Fl</t>
+    <t xml:space="preserve">Electronic Controller - Bo&amp;Fl</t>
   </si>
   <si>
     <t xml:space="preserve">1485.00</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">OLECBR20</t>
   </si>
   <si>
-    <t xml:space="preserve">Oval 20 - blank ring</t>
+    <t xml:space="preserve">Oval 20 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">420.00</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">OLECBR25</t>
   </si>
   <si>
-    <t xml:space="preserve">Oval 25 - blank ring.</t>
+    <t xml:space="preserve">Oval 25 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">505.00</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">OLECBR30</t>
   </si>
   <si>
-    <t xml:space="preserve">Oval 30 - blank ring.</t>
+    <t xml:space="preserve">Oval 30 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">560.00</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">OLHBP</t>
   </si>
   <si>
-    <t xml:space="preserve">Pyrometer for hot box.</t>
+    <t xml:space="preserve">Pyrometer For Hot Box</t>
   </si>
   <si>
     <t xml:space="preserve">280.00</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">OLIRTS1823</t>
   </si>
   <si>
-    <t xml:space="preserve">Ignit Ring &amp; Thermo TB-18&amp;23'S</t>
+    <t xml:space="preserve">Ignit Ring &amp; Thermo Tb-18&amp;23'S</t>
   </si>
   <si>
     <t xml:space="preserve">465.00</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">OLIRTS28</t>
   </si>
   <si>
-    <t xml:space="preserve">Ignit. Ring &amp; Thermo. TB-28'S</t>
+    <t xml:space="preserve">Ignit. Ring &amp; Thermo. Tb-28'S</t>
   </si>
   <si>
     <t xml:space="preserve">540.00</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">OLTBBR18</t>
   </si>
   <si>
-    <t xml:space="preserve">Torch bearer 18 - blank ring</t>
+    <t xml:space="preserve">Torch Bearer 18 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">270.00</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">OLTBBR23</t>
   </si>
   <si>
-    <t xml:space="preserve">Torch bearer 23 - blank ring</t>
+    <t xml:space="preserve">Torch Bearer 23 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">310.00</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">OLTBBR28</t>
   </si>
   <si>
-    <t xml:space="preserve">Torch bearer 28 - blank ring.</t>
+    <t xml:space="preserve">Torch Bearer 28 - Blank Ring</t>
   </si>
   <si>
     <t xml:space="preserve">430.00</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">OES</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic ELECTRO SITTER Electronic Controller to Replace Dawson Kiln Si</t>
+    <t xml:space="preserve">Olympic Electro Sitter To Replace Dawson Kiln Sitters</t>
   </si>
   <si>
     <t xml:space="preserve">1155.00</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">OL1214120</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC 1214-120: Cone 4, Top Loading 120 Volt Electric Kiln OLYMPIC 1</t>
+    <t xml:space="preserve">Olympic 1214-120: Cone 4, 120 Volt Electric Kiln w/3 Key</t>
   </si>
   <si>
     <t xml:space="preserve">1849.00</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">OL1214ERAKU</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1214 Electric Raku Kiln Now YOU can create beautiful raku piec</t>
+    <t xml:space="preserve">Olympic 1214 Electric Raku Kiln With 12 key Controller</t>
   </si>
   <si>
     <t xml:space="preserve">2199.00</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">OL129</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC 129 120 Volt Electric Kiln : Cone 6, Top Loading 120 Volt Elec</t>
+    <t xml:space="preserve">Olympic 129: Cone 6, Top Loading 120 Volt Electric Kiln with Genesis S</t>
   </si>
   <si>
     <t xml:space="preserve">1509.00</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">OL1414HE</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC 1414HE KILN Available in 240v or 208v. Comes equipped with Bar</t>
+    <t xml:space="preserve">Olympic 1414HE Kiln with 3 Key Controller</t>
   </si>
   <si>
     <t xml:space="preserve">1749.00</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">OL146GFETLC</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Kilns GLASS FUSING KILN Model - 146GFETLC OLYMPIC KILN Model -</t>
+    <t xml:space="preserve">Olympic Kilns - 146Gfetlc 120V Glass Fusing Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">1915.00</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">OL146GFETLCFK</t>
   </si>
   <si>
-    <t xml:space="preserve">This is a OLYMPIC KILN 146GFETLC FURNITURE KIT 2 full shelves, 3 : 1/2</t>
+    <t xml:space="preserve">Olympic Kilns 146Gfetlc Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">120.00</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">OL1818</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1818 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 1818 Stackable Electric Kiln With KilnStar Controller : 2.63 C</t>
   </si>
   <si>
     <t xml:space="preserve">2349.00</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">OL1818H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1818HE "Stackable" Electric Kiln with V6-CF Electronic Control</t>
+    <t xml:space="preserve">Olympic 1818H Stackable Electric Kiln With 12 Key Controller</t>
   </si>
   <si>
     <t xml:space="preserve">2437.00</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">OL1823</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1823 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 1823 Stackable Electric Kiln With 12 key Controller Cone 8</t>
   </si>
   <si>
     <t xml:space="preserve">2599.00</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">OL1823ERAKU</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Electric Raku Kiln 1823e 3.29 cubic feet , cone 8 max temperat</t>
+    <t xml:space="preserve">Olympic 1823 Electric Raku Kiln With 12 key Controller</t>
   </si>
   <si>
     <t xml:space="preserve">2999.00</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">OL1823H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1823H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 1823H Stackable Electric Kiln With KilnStar Controller : 3.29 </t>
   </si>
   <si>
     <t xml:space="preserve">2679.00</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">OL1827</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1827 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 1827 Stackable Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">2785.00</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">OL1827G</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing ceramic kilns, gas kilns, Olympic Kilns. This is an O</t>
+    <t xml:space="preserve">Olympic 1827-Torch Bearer Kiln / Natural Gas Or Propane With Burners A</t>
   </si>
   <si>
     <t xml:space="preserve">2419.00</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">OL1827H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 1827H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 1827H Stackable Electric Kiln 3.95 Cu. Ft: Cone 10</t>
   </si>
   <si>
     <t xml:space="preserve">2899.00</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">OL186GFETLC</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC KILN 186GFETLC Model - Square 186GFETLC - 120 volt, inside dim</t>
+    <t xml:space="preserve">Olympic Kilns 186GFETLC Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">2629.00</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">OL18RAKU</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC 18" RAKU KILN /NATURAL GAS or PROPANE With Burners and Ignitio</t>
+    <t xml:space="preserve">Olympic 18" Raku Kiln /Natural Gas Or Propane With Burners And Ignitio</t>
   </si>
   <si>
     <t xml:space="preserve">2769.00</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">OL2318</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2318 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 2318 Stackable Electric Digital Kiln 4.7 Cu. Ft: Cone 8</t>
   </si>
   <si>
     <t xml:space="preserve">3219.00</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">OL2318H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2318H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2318H Stackable Electric Kiln With KilnStar Controller : 4.7 C</t>
   </si>
   <si>
     <t xml:space="preserve">3249.00</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">OL2323</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2323 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 2323 Stackable Digital Electric Kiln 5.83 Cu. Ft: Cone 4</t>
   </si>
   <si>
     <t xml:space="preserve">3260.00</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">OL2323H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2323H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2323H Stackable Electric Kiln With KilnStar Controller : 5.83 </t>
   </si>
   <si>
     <t xml:space="preserve">3689.00</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">OL2327</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2327 "Stackable" Electric Kiln with V6-CF Electronic Controlle</t>
+    <t xml:space="preserve">Olympic 2327 Stackable Electric Kiln With KilnStar Controller : 7 Cu. </t>
   </si>
   <si>
     <t xml:space="preserve">3759.00</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">OL2327G</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing gas kilns, raku kilns, Olympic Kilns. This is a 2327-</t>
+    <t xml:space="preserve">2327-Olympic Torch Bearer Kiln /Natural Gas Or Propane With Burners An</t>
   </si>
   <si>
     <t xml:space="preserve">3169.00</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">OL2327H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns : 2323H "Stackable" Electric Kiln with V6-CF Electronic </t>
+    <t xml:space="preserve">Olympic 2327H Stackable Electric Kiln 7 Cu. Ft Cone 10</t>
   </si>
   <si>
     <t xml:space="preserve">3969.00</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">OL2331G</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing gas kilns, raku kilns Olympic Kilns. This is a 2331-O</t>
+    <t xml:space="preserve">2331-Olympic Torch Bearer Kiln /Natural Gas Or Propane With Burners An</t>
   </si>
   <si>
     <t xml:space="preserve">3399.00</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">OL2331H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2331H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2331H Stackable Electric Kiln With KilnStar Controller : 8.17 </t>
   </si>
   <si>
     <t xml:space="preserve">4199.00</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">OL23RAKU</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing gas kilns and raku kilns, Olympic Kilns. This is a OL</t>
+    <t xml:space="preserve">Olympic 23" Raku Kiln /Natural Gas Or Propane With Burners And Ignitio</t>
   </si>
   <si>
     <t xml:space="preserve">3859.00</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">OL2818H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2818H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2818H Stackable Electric Kiln With KilnStar Controller : 6.67 </t>
   </si>
   <si>
     <t xml:space="preserve">3949.00</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">OL2823H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2823H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2823H Stackable Electric Kiln With KilnStar Controller : 8.34 </t>
   </si>
   <si>
     <t xml:space="preserve">4239.00</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">OL2827G</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing gas kilns raku kilns. This is a 2827-OLYMPIC TORCH BE</t>
+    <t xml:space="preserve">2827-Olympic Torch Bearer Kiln / Natural Gas Or Propane With Burners A</t>
   </si>
   <si>
     <t xml:space="preserve">4129.00</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">OL2827H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2827H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2827H Stackable Digital Electric Kiln 10 Cu. Ft: Cone 10</t>
   </si>
   <si>
     <t xml:space="preserve">4629.00</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">OL2831G</t>
   </si>
   <si>
-    <t xml:space="preserve">2831-OLYMPIC TORCH BEARER KILN /NATURAL GAS or PROPANE With Burners an</t>
+    <t xml:space="preserve">2831-Olympic Torch Bearer Kiln Natural Gas or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">4399.00</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">OL2831H</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 2831H "Stackable" Electric Kiln with V6-CF Electronic Controll</t>
+    <t xml:space="preserve">Olympic 2831H Digital Stackable Electric Kiln 11.67 Cu. Ft: Cone 10</t>
   </si>
   <si>
     <t xml:space="preserve">5079.00</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">OL28RAKU</t>
   </si>
   <si>
-    <t xml:space="preserve">n OLYMPIC 28" RAKU KILN / NATURAL GAS or PROPANE With Burners and Igni</t>
+    <t xml:space="preserve">Olympic 28" Raku Kiln / Natural Gas Or Propane With Burners And Igniti</t>
   </si>
   <si>
     <t xml:space="preserve">4879.00</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">OLCHAMP</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC CHAMP GLASS KILN Win every time you fire with Olympic's Champ </t>
+    <t xml:space="preserve">Olympic Champ Glass Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">1299.00</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">OLCHAMPXL</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC CHAMP XL GLASS KILN Looking for the glass kiln that will make </t>
+    <t xml:space="preserve">Olympic Champ Xl Glass Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">1389.00</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">OLDD12</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing Olympic kilns. This is an OLYMPIC DD12 KILN (DOWNDRAF</t>
+    <t xml:space="preserve">Olympic Kilns DD12 Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">11130.00</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">OLDD14</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing Olympic Kilns. This is an OLYMPIC KILN DD14 - DOWNDRA</t>
+    <t xml:space="preserve">Olympic Kiln DD14 - Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">13030.00</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">OLDD17</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing Olympic Kilns. This is a OLYMPIC KILN DD17 - DOWNDRAF</t>
+    <t xml:space="preserve">Olympic Kiln DD17 - Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">14905.00</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">OLDD20</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing ceramic kilns, Olympic Kilns. This is an OLYMPIC KILN</t>
+    <t xml:space="preserve">Olympic Kiln DD20 - Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">17820.00</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">OLDD24</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC DD24 - DOWNDRAFT KILN / NATURAL GAS Please call for special di</t>
+    <t xml:space="preserve">Olympic Kilns DD24 - Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">20500.00</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">OLDD30</t>
   </si>
   <si>
-    <t xml:space="preserve">You are browsing ceramic kilns, Olympic Kilns. This is an Olympic DD30</t>
+    <t xml:space="preserve">Olympic Kilns DD30 - Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">22990.00</t>
@@ -725,6 +725,9 @@
     <t xml:space="preserve">OLDD40</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Kilns DD40-Downdraft Kiln Gas Or Propane</t>
+  </si>
+  <si>
     <t xml:space="preserve">28130.00</t>
   </si>
   <si>
@@ -734,7 +737,7 @@
     <t xml:space="preserve">OLDD9</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC KILNS DD9-DOWNDRAFT KILN Gas or Propane This is an Olympic DD9</t>
+    <t xml:space="preserve">Olympic Kilns DD9-Downdraft Kiln Gas Or Propane</t>
   </si>
   <si>
     <t xml:space="preserve">10650.00</t>
@@ -746,7 +749,7 @@
     <t xml:space="preserve">OLDDBB</t>
   </si>
   <si>
-    <t xml:space="preserve">Powered Blower Burner FOR OLYMPIC DOWNDRAFT KILNS Blower Burner - Forc</t>
+    <t xml:space="preserve">Blower Burner For Olympic Downdraft Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1727.00</t>
@@ -761,7 +764,7 @@
     <t xml:space="preserve">OLDDDP10</t>
   </si>
   <si>
-    <t xml:space="preserve">DIGITAL PYROMETER FOR OLYMPIC KILNS - The TPI 343 is a Dual Input K-Ty</t>
+    <t xml:space="preserve">Digital Pyrometer For Olympic Gas Kilns - w/10" Thermocouple</t>
   </si>
   <si>
     <t xml:space="preserve">290.00</t>
@@ -773,7 +776,7 @@
     <t xml:space="preserve">OLDDEC</t>
   </si>
   <si>
-    <t xml:space="preserve">ELECTRONIC Shut-Off INCLUDING VALVE FOR OLYMPIC GAS KILNS including Do</t>
+    <t xml:space="preserve">120V/20A Electronic High Limit Shut Off Including Valve For Olympic Ga</t>
   </si>
   <si>
     <t xml:space="preserve">1452.00</t>
@@ -782,13 +785,13 @@
     <t xml:space="preserve">Accessories: High Limit Controller</t>
   </si>
   <si>
-    <t xml:space="preserve">electronic shut-off w/ valve; closest item in the 2026 list</t>
+    <t xml:space="preserve">listing is the 120V/20A electronic high-limit shut-off with valve; the list has one High Limit Controller price</t>
   </si>
   <si>
     <t xml:space="preserve">OLDDGH</t>
   </si>
   <si>
-    <t xml:space="preserve">Galvanized steel kiln hood for olympic downdraft models.</t>
+    <t xml:space="preserve">Galvanized Steel Hood For Olympic Downdraft Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1865.00</t>
@@ -800,7 +803,7 @@
     <t xml:space="preserve">OLDDSH</t>
   </si>
   <si>
-    <t xml:space="preserve">Stainless steel hood for Olympic downdraft kilns.</t>
+    <t xml:space="preserve">Stainless Steel Hood For Olympic Downdraft Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">2100.00</t>
@@ -812,7 +815,7 @@
     <t xml:space="preserve">OLDM1818HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 1818HE: 2.63 cu. ft. : Cone 10 with RTC-1000 D</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 1818He: 2.63 Cu. Ft. : Cone 10 With Rtc-1000 D</t>
   </si>
   <si>
     <t xml:space="preserve">2799.00</t>
@@ -824,7 +827,7 @@
     <t xml:space="preserve">OLDM1823HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 1823HE: 3.29 cu. ft. : Cone 10 with RTC-1000 D</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 1823HE: 3.29 Cu. Ft. : Cone 10</t>
   </si>
   <si>
     <t xml:space="preserve">3099.00</t>
@@ -836,7 +839,7 @@
     <t xml:space="preserve">OLDM2318HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2318HE: 4.7 cu. ft. : Cone 10 with RTC-1000 Di</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2318He: 4.7 Cu. Ft. : Cone 10 With Rtc-1000 Di</t>
   </si>
   <si>
     <t xml:space="preserve">3649.00</t>
@@ -848,7 +851,7 @@
     <t xml:space="preserve">OLDM2323HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2323HE: 5.83 cu. ft. : Cone 10 with RTC-1000 D</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2323He: 5.83 Cu. Ft. : Cone 10 With Rtc-1000 D</t>
   </si>
   <si>
     <t xml:space="preserve">4079.00</t>
@@ -860,7 +863,7 @@
     <t xml:space="preserve">OLDM2327HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2327HE: 7 cu. ft. : Cone 10 with 12 Key Contro</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2327He: 7 Cu. Ft. Cone 10 Digital</t>
   </si>
   <si>
     <t xml:space="preserve">4299.00</t>
@@ -872,7 +875,7 @@
     <t xml:space="preserve">OLDM2523HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2523HE OVAL: 10 cu. ft. : Cone 10 with RTC-100</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2523He Oval: 10 Cu. Ft. : Cone 10 With Rtc-100</t>
   </si>
   <si>
     <t xml:space="preserve">5435.00</t>
@@ -884,7 +887,7 @@
     <t xml:space="preserve">OLDM2818HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2818HE: 6.67 cu. ft. : Cone 10 with RTC-1000 D</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2818He: 6.67 Cu. Ft. : Cone 10 With Rtc-1000 D</t>
   </si>
   <si>
     <t xml:space="preserve">4349.00</t>
@@ -896,7 +899,7 @@
     <t xml:space="preserve">OLDM2823HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2823HE: 8.34 cu. ft. : Cone 10 with RTC-1000 D</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2823He: 8.34 Cu. Ft. : Cone 10 With Rtc-1000 D</t>
   </si>
   <si>
     <t xml:space="preserve">4749.00</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">OLDM2827HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 2827HE: 10 cu. ft. : Cone 10 with RTC-1000 Dig</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 2827He: 10 Cu. Ft. : Cone 10 With Rtc-1000 Dig</t>
   </si>
   <si>
     <t xml:space="preserve">5019.00</t>
@@ -920,7 +923,7 @@
     <t xml:space="preserve">OLDM3018HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 3018HE OVAL: 12.2 cu. ft. : Cone 10 with RTC-1</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 3018HE</t>
   </si>
   <si>
     <t xml:space="preserve">5849.00</t>
@@ -932,7 +935,7 @@
     <t xml:space="preserve">OLDM3023HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DUAL MEDIA KILN 3023HE OVAL: 14.9 cu. ft. : Cone 10 with RTC-1</t>
+    <t xml:space="preserve">Olympic Dual Media Kiln 3023He Oval: 14.9 Cu. Ft. : Cone 10 With Rtc-1</t>
   </si>
   <si>
     <t xml:space="preserve">6279.00</t>
@@ -944,13 +947,13 @@
     <t xml:space="preserve">OLDP</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Digital Pyrometer with two 6" Type K thermocouples The digital</t>
+    <t xml:space="preserve">Olympic Digital Pyrometer with two 6" Type K thermocouples</t>
   </si>
   <si>
     <t xml:space="preserve">OLF1414HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Freedom Series Kilns Order your Olympic Freedom Kiln Package f</t>
+    <t xml:space="preserve">Olympic Freedom 1414He Kiln Package: Cone 10, Electronic Control With </t>
   </si>
   <si>
     <t xml:space="preserve">2695.00</t>
@@ -962,7 +965,7 @@
     <t xml:space="preserve">OLF1823HE</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FREEDOM 1823HE KILN PACKAGE Olympic Freedom Series Kilns Order</t>
+    <t xml:space="preserve">Olympic Freedom 1823He Kiln Package: Cone 10 Package</t>
   </si>
   <si>
     <t xml:space="preserve">Kilns: F1823HE Pkg. (base = KilnStar)</t>
@@ -971,7 +974,7 @@
     <t xml:space="preserve">OLF2323HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns Freedom Series Order your Olympic Freedom Kiln Package f</t>
+    <t xml:space="preserve">Olympic Freedom 2323He Kiln Package With Vent, Furniture Kit And More</t>
   </si>
   <si>
     <t xml:space="preserve">4519.00</t>
@@ -983,7 +986,7 @@
     <t xml:space="preserve">OLF2327HE</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FREEDOM 2327HE KILN PACKAGE Olympic Freedom Series Kilns Order</t>
+    <t xml:space="preserve">Olympic Freedom 2327He Kiln Package: With Vent, Furniture Kit And More</t>
   </si>
   <si>
     <t xml:space="preserve">5279.00</t>
@@ -995,6 +998,9 @@
     <t xml:space="preserve">OLF2527HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Freedom 2527He Kiln Package: with Vent, Furniture Kit and More</t>
+  </si>
+  <si>
     <t xml:space="preserve">6199.00</t>
   </si>
   <si>
@@ -1004,6 +1010,9 @@
     <t xml:space="preserve">OLF2823HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Freedom 2823He Kiln Package: with Vent, Furniture Kit and More</t>
+  </si>
+  <si>
     <t xml:space="preserve">5660.00</t>
   </si>
   <si>
@@ -1013,6 +1022,9 @@
     <t xml:space="preserve">OLF2827HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Freedom 2827HE Kiln Package: Cone 10, Electronic Control With </t>
+  </si>
+  <si>
     <t xml:space="preserve">6119.00</t>
   </si>
   <si>
@@ -1022,7 +1034,7 @@
     <t xml:space="preserve">OLFL12</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-12 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-12 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">9199.00</t>
@@ -1034,7 +1046,7 @@
     <t xml:space="preserve">OLFL17</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-17 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-17 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">11499.00</t>
@@ -1046,7 +1058,7 @@
     <t xml:space="preserve">OLFL20</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-20 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-20 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">12699.00</t>
@@ -1058,7 +1070,7 @@
     <t xml:space="preserve">OLFL24</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL-24 Front Loading Electric Kiln The Olympic FL-24 is a large</t>
+    <t xml:space="preserve">Olympic FL-24 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">14899.00</t>
@@ -1070,7 +1082,7 @@
     <t xml:space="preserve">OLFL27</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-27 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-27 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">16999.00</t>
@@ -1082,7 +1094,7 @@
     <t xml:space="preserve">OLFL31</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-31 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-31 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">19099.00</t>
@@ -1094,7 +1106,7 @@
     <t xml:space="preserve">OLFL53</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-53 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-53 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">26899.00</t>
@@ -1106,7 +1118,7 @@
     <t xml:space="preserve">OLFL55</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-5 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gra</t>
+    <t xml:space="preserve">Olympic FL-5.5 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">7059.00</t>
@@ -1121,7 +1133,7 @@
     <t xml:space="preserve">OLFL8</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-8 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gra</t>
+    <t xml:space="preserve">Olympic FL-8 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">7899.00</t>
@@ -1133,7 +1145,7 @@
     <t xml:space="preserve">OLGF2ETLC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns GF2ETLC Glass Fusing Kiln OLYMPIC KILN Model - glass fus</t>
+    <t xml:space="preserve">Olympic Kilns GF2ETLC Glass Fusing Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">3019.00</t>
@@ -1148,7 +1160,7 @@
     <t xml:space="preserve">OLGF3ETLC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic GF3ETLC Glass Fusing Kiln OLYMPIC Model GF3ETLC Glass fusing k</t>
+    <t xml:space="preserve">Olympic GF3ETLC Glass Fusing Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">3239.00</t>
@@ -1160,7 +1172,7 @@
     <t xml:space="preserve">OLHB</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC HOTBOX : Cone 10, Top Loading 120 Volt Electric Kiln Now inclu</t>
+    <t xml:space="preserve">Olympic Hotbox : Cone 10, Top Loading 120 Volt Electric Kiln with Gene</t>
   </si>
   <si>
     <t xml:space="preserve">1149.00</t>
@@ -1172,7 +1184,7 @@
     <t xml:space="preserve">OLHB64</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC HB64 : Cone 10, Top Loading 120 Volt Electric Kiln OLYMPIC HOT</t>
+    <t xml:space="preserve">Olympic HB64 : Cone 10, Top Loading 120 Volt Electric Kiln w/3 Key</t>
   </si>
   <si>
     <t xml:space="preserve">1049.00</t>
@@ -1184,7 +1196,7 @@
     <t xml:space="preserve">OLHB84</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC HB84 : Cone 10, Top Loading 120 Volt Electric Kiln Now include</t>
+    <t xml:space="preserve">Olympic HB84 : Cone 10, Top Loading 120 Volt Electric Kiln with Genesi</t>
   </si>
   <si>
     <t xml:space="preserve">1189.00</t>
@@ -1196,7 +1208,7 @@
     <t xml:space="preserve">OLHB86</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC HB86 : Cone 10, Top Loading 120 Volt Electric Kiln OLYMPIC HB8</t>
+    <t xml:space="preserve">Olympic HB86 : Cone 10, Top Loading 120 Volt Electric Kiln Genesis Spa</t>
   </si>
   <si>
     <t xml:space="preserve">1209.00</t>
@@ -1208,7 +1220,7 @@
     <t xml:space="preserve">OLHB86V</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot Box 86 equipped with pyrometer and infinite switch Model - HB86P V</t>
+    <t xml:space="preserve">Olympic HB86P Vitrigraph Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">1449.00</t>
@@ -1220,7 +1232,7 @@
     <t xml:space="preserve">OLHB89</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC HB89 : Cone 10, Top Loading 120 Volt Electric Kiln: Now includ</t>
+    <t xml:space="preserve">Olympic HB89 : Cone 10, Top Loading 120 Volt Electric Kiln with Genesi</t>
   </si>
   <si>
     <t xml:space="preserve">1329.00</t>
@@ -1232,7 +1244,7 @@
     <t xml:space="preserve">OLHBFK</t>
   </si>
   <si>
-    <t xml:space="preserve">FURNITURE KIT FOR Olympic HOTBOX KILN</t>
+    <t xml:space="preserve">Furniture Kit For Olympic Hotbox Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">82.00</t>
@@ -1244,7 +1256,7 @@
     <t xml:space="preserve">OLHLC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns Optional High Limit Controller for Gas Kilns Olympic Kil</t>
+    <t xml:space="preserve">Olympic Kilns Optional High Limit Controller for Gas Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1399.00</t>
@@ -1256,7 +1268,7 @@
     <t xml:space="preserve">OLMAS1818HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Dreams Come True with Olympic's Medallion Artist Series Looking for wa</t>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas1818He : 2.63 Cu. Ft Cone 10: 12Key</t>
   </si>
   <si>
     <t xml:space="preserve">2139.00</t>
@@ -1268,6 +1280,9 @@
     <t xml:space="preserve">OLMAS1823HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas1823He : 3.29 Cu. Ft Cone 10: 12Key</t>
+  </si>
+  <si>
     <t xml:space="preserve">2249.00</t>
   </si>
   <si>
@@ -1277,13 +1292,16 @@
     <t xml:space="preserve">OLMAS2323HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas2323He : 5.83 Cu. Ft Cone 10: 12Key</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilns: MAS 2323HE (base = KilnStar)</t>
   </si>
   <si>
     <t xml:space="preserve">OLMAS2327HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Medallion Artist SeriesDreams Come True with Olympic's Medallion Artis</t>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas2327He : 7 Cu. Ft Cone 10: 12 Key E</t>
   </si>
   <si>
     <t xml:space="preserve">3329.00</t>
@@ -1295,7 +1313,7 @@
     <t xml:space="preserve">OLMAS2823HE</t>
   </si>
   <si>
-    <t xml:space="preserve">Medallion Artist Series Dreams Come True with Olympic's Medallion Arti</t>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas2823He : 8.34 Cu. Ft Cone 10: 12Key</t>
   </si>
   <si>
     <t xml:space="preserve">3719.00</t>
@@ -1310,6 +1328,9 @@
     <t xml:space="preserve">OLMAS2827HE</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic Medallion Artist Series Mas2827He :10 Cu. Ft Cone 10: 12Key El</t>
+  </si>
+  <si>
     <t xml:space="preserve">3989.00</t>
   </si>
   <si>
@@ -1319,7 +1340,7 @@
     <t xml:space="preserve">OLO2018H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2018H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2018H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">4035.00</t>
@@ -1331,7 +1352,7 @@
     <t xml:space="preserve">OLO2023H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2023H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2023H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">4689.00</t>
@@ -1346,7 +1367,7 @@
     <t xml:space="preserve">OLO2027H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2027H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2027H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">4329.00</t>
@@ -1358,7 +1379,7 @@
     <t xml:space="preserve">OLO2518H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2518H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2518H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">4469.00</t>
@@ -1370,7 +1391,7 @@
     <t xml:space="preserve">OLO2523H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2523H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2523H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">4979.00</t>
@@ -1382,7 +1403,7 @@
     <t xml:space="preserve">OLO2527H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2527H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2527H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">5419.00</t>
@@ -1394,7 +1415,7 @@
     <t xml:space="preserve">OLO2531H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 2531H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 2531H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">5890.00</t>
@@ -1406,7 +1427,7 @@
     <t xml:space="preserve">OLO3018H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 3018H Note: shown is the taller 3027 Mode</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 3018H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">5469.00</t>
@@ -1418,7 +1439,7 @@
     <t xml:space="preserve">OLO3023H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 3023H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 3023H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">5859.00</t>
@@ -1430,7 +1451,7 @@
     <t xml:space="preserve">OLO3027H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 3027H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 3027H With KilnStar Electronic Controller</t>
   </si>
   <si>
     <t xml:space="preserve">6439.00</t>
@@ -1442,7 +1463,7 @@
     <t xml:space="preserve">OLO3031H</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC Electric OVAL KILN : 3031H Model comes with stand, peephole pl</t>
+    <t xml:space="preserve">Olympic Oval Kiln : 3031H With KilnStar Controller</t>
   </si>
   <si>
     <t xml:space="preserve">6915.00</t>
@@ -1454,7 +1475,7 @@
     <t xml:space="preserve">OLODT</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC DOLL /TEST Mini Oval 120 Volt Electric Kiln : Cone 10, Top Loa</t>
+    <t xml:space="preserve">Olympic Doll /Test Mini Oval Kiln: Cone 10, Top Loading 120 Volt Elect</t>
   </si>
   <si>
     <t xml:space="preserve">1419.00</t>
@@ -1466,7 +1487,7 @@
     <t xml:space="preserve">OLPEEP</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic peephole plug.</t>
+    <t xml:space="preserve">Olympic Peephole Plug</t>
   </si>
   <si>
     <t xml:space="preserve">17.00</t>
@@ -1478,7 +1499,7 @@
     <t xml:space="preserve">OLTL20E</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Top Loading Commercial Electric Kiln TL20 WithV6-CF Electronic</t>
+    <t xml:space="preserve">Olympic Top Loading Commercial Electric Kiln TL20 With V6-CF Controlle</t>
   </si>
   <si>
     <t xml:space="preserve">9529.00</t>
@@ -1490,7 +1511,7 @@
     <t xml:space="preserve">OLTL5432E</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Top Loading Commercial Electric Kiln TL20 Olympic Top Loading </t>
+    <t xml:space="preserve">Olympic Top Loading Commercial Electric Kiln TL5432E</t>
   </si>
   <si>
     <t xml:space="preserve">17599.00</t>
@@ -1505,7 +1526,7 @@
     <t xml:space="preserve">OLTRAV</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC TRAVELER KILN: Glass and Ceramic Combo with 3 Key Electronic C</t>
+    <t xml:space="preserve">Olympic Traveler Kiln: Glass And Ceramic Combo With 3 Key Electronic C</t>
   </si>
   <si>
     <t xml:space="preserve">1789.00</t>
@@ -1517,7 +1538,7 @@
     <t xml:space="preserve">SPIFL12</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL12 FRONT LOADING KILN PACKAGE We have taken the most request</t>
+    <t xml:space="preserve">Olympic FL12 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">12376.00</t>
@@ -1529,7 +1550,7 @@
     <t xml:space="preserve">SPIFL17</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL17 Complete FRONT LOADING KILN PACKAGE These are commercial </t>
+    <t xml:space="preserve">Olympic FL17 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">14742.00</t>
@@ -1538,7 +1559,7 @@
     <t xml:space="preserve">SPIFL20</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL20 Complete FRONT LOADING KILN PACKAGE This is a 20 cubic fe</t>
+    <t xml:space="preserve">Olympic FL20 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">16522.00</t>
@@ -1547,7 +1568,7 @@
     <t xml:space="preserve">SPIFL24</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL24 Complete FRONT LOADING KILN PACKAGE We have taken the mos</t>
+    <t xml:space="preserve">Olympic FL24 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">18207.00</t>
@@ -1556,7 +1577,7 @@
     <t xml:space="preserve">SPIFL27</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL27 Complete FRONT LOADING KILN PACKAGE This is a commercial </t>
+    <t xml:space="preserve">Olympic FL27 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">21742.00</t>
@@ -1565,7 +1586,7 @@
     <t xml:space="preserve">SPIFL31</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL31 Complete FRONT LOADING KILN PACKAGE These are commercial </t>
+    <t xml:space="preserve">Olympic FL31 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">24507.00</t>
@@ -1574,7 +1595,7 @@
     <t xml:space="preserve">SPIFL53</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL53 Complete FRONT LOADING KILN PACKAGE These are commercial </t>
+    <t xml:space="preserve">Olympic FL53 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">35245.00</t>
@@ -1583,7 +1604,7 @@
     <t xml:space="preserve">SPIFL8</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL8 FRONT LOADING KILN PACKAGE These are commercial grade fron</t>
+    <t xml:space="preserve">Olympic FL8 Complete Front Loading Kiln Package</t>
   </si>
   <si>
     <t xml:space="preserve">10959.00</t>
@@ -1592,7 +1613,7 @@
     <t xml:space="preserve">OLFL42</t>
   </si>
   <si>
-    <t xml:space="preserve">OLYMPIC FL-42 FRONT LOADING KILN Olympic Kilns FL Series Commercial Gr</t>
+    <t xml:space="preserve">Olympic FL-42 Front Loading Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">25199.00</t>
@@ -1604,7 +1625,7 @@
     <t xml:space="preserve">OLSTYPE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic S-type Thermocouple Upgrade Product option do not apply</t>
+    <t xml:space="preserve">Olympic S-type Thermocouple Upgrade</t>
   </si>
   <si>
     <t xml:space="preserve">599.00</t>
@@ -1616,7 +1637,7 @@
     <t xml:space="preserve">OLTL20FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic TL20 Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">Olympic TL20 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1188.75</t>
@@ -1628,7 +1649,7 @@
     <t xml:space="preserve">OLHB89SHELF</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic HB89 Extra Shelf Product option do not apply</t>
+    <t xml:space="preserve">Olympic HB89 Extra Shelf</t>
   </si>
   <si>
     <t xml:space="preserve">26.00</t>
@@ -1640,7 +1661,7 @@
     <t xml:space="preserve">OLK3K</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Electro-Sitter : 3 Key Base Model Product option do not apply</t>
+    <t xml:space="preserve">Olympic Electro-Sitter : 3 Key Base Model</t>
   </si>
   <si>
     <t xml:space="preserve">855.00</t>
@@ -1652,7 +1673,7 @@
     <t xml:space="preserve">OL18RAFK</t>
   </si>
   <si>
-    <t xml:space="preserve">18 Raku Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">18 Raku Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">326.25</t>
@@ -1664,7 +1685,7 @@
     <t xml:space="preserve">OL23RAFK</t>
   </si>
   <si>
-    <t xml:space="preserve">23 Raku Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">23 Raku Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">577.50</t>
@@ -1676,7 +1697,7 @@
     <t xml:space="preserve">OL28RAFK</t>
   </si>
   <si>
-    <t xml:space="preserve">28 Raku Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">28 Raku Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">645.00</t>
@@ -1688,7 +1709,7 @@
     <t xml:space="preserve">OL1823EFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture Kit for OL1823ERAKU product option do not apply</t>
+    <t xml:space="preserve">Furniture Kit for OL1823ERAKU</t>
   </si>
   <si>
     <t xml:space="preserve">210.00</t>
@@ -1700,7 +1721,7 @@
     <t xml:space="preserve">OL1214ERAFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Furniture Kit for OL1214ERAKU product option do not apply</t>
+    <t xml:space="preserve">Furniture Kit for OL1214ERAKU</t>
   </si>
   <si>
     <t xml:space="preserve">183.75</t>
@@ -1712,7 +1733,7 @@
     <t xml:space="preserve">OL1827GFK</t>
   </si>
   <si>
-    <t xml:space="preserve">1827 Torchbearer Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">1827 TorcHBearer Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">217.50</t>
@@ -1724,7 +1745,7 @@
     <t xml:space="preserve">OLDD12FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD12 Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">Olympic DD12 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">821.25</t>
@@ -1736,7 +1757,7 @@
     <t xml:space="preserve">OLDD9FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD9 Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">Olympic DD9 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">915.00</t>
@@ -1748,7 +1769,7 @@
     <t xml:space="preserve">OLDD14FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD14 Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">Olympic DD14 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">877.50</t>
@@ -1760,7 +1781,7 @@
     <t xml:space="preserve">OL2018BR</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add a 4.5" blank ring: Adds 1.98 cu ft. Product option do not</t>
+    <t xml:space="preserve">Olympic: ADD a 4.5" blank ring: ADDs 1.98 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">SKU says 2018 but "adds 1.98 cu ft" reads like a 25" oval ring</t>
@@ -1769,7 +1790,7 @@
     <t xml:space="preserve">OL25HOFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Add the Oval 25H Furniture Kit product option do not apply</t>
+    <t xml:space="preserve">Olympic ADD the Oval 25H Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">742.50</t>
@@ -1781,7 +1802,7 @@
     <t xml:space="preserve">OL30HEFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the Oval 30H Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">ADD the Oval 30H Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">975.00</t>
@@ -1793,7 +1814,7 @@
     <t xml:space="preserve">OLDD17FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD17 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic DD17 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: DownDraft (DD) Gas Kilns — DD17</t>
@@ -1802,7 +1823,7 @@
     <t xml:space="preserve">OLDD20FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD20 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic DD20 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1361.25</t>
@@ -1814,7 +1835,7 @@
     <t xml:space="preserve">OLHLC120</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 120V High Limit Controller Product option do not apply</t>
+    <t xml:space="preserve">Olympic 120V High Limit Controller</t>
   </si>
   <si>
     <t xml:space="preserve">1320.00</t>
@@ -1826,7 +1847,7 @@
     <t xml:space="preserve">OLDD24FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD24 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic DD24 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1413.75</t>
@@ -1838,7 +1859,7 @@
     <t xml:space="preserve">OLDD30FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD30 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic DD30 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1545.00</t>
@@ -1850,7 +1871,7 @@
     <t xml:space="preserve">OLDD40FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic DD40 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic DD40 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1710.00</t>
@@ -1862,7 +1883,7 @@
     <t xml:space="preserve">OLTRAVFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Traveler Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Traveler Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">176.25</t>
@@ -1874,7 +1895,7 @@
     <t xml:space="preserve">OLLPR18</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add Low Pressure Regulator for 18" Gas Kiln Product option do</t>
+    <t xml:space="preserve">Olympic: ADD Low Pressure Regulator for 18" Gas Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">155.00</t>
@@ -1886,7 +1907,7 @@
     <t xml:space="preserve">OLGH</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Galvanized Hood for DD Gas Kilns Product option do not apply</t>
+    <t xml:space="preserve">Olympic Galvanized Hood for DD Gas Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1695.00</t>
@@ -1895,7 +1916,7 @@
     <t xml:space="preserve">OLHSSUPD</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 36"x36" Stainless Vent Hood for 18" and 23" Gas Kilns Product </t>
+    <t xml:space="preserve">Olympic 36"x36" Stainless Vent Hood for 18" and 23" Gas Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1525.00</t>
@@ -1907,7 +1928,7 @@
     <t xml:space="preserve">OLSSH4040</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 40"x40" Stainless Vent Hood for 28" Gas Kilns Product option d</t>
+    <t xml:space="preserve">Olympic 40"x40" Stainless Vent Hood for 28" Gas Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">1670.00</t>
@@ -1919,13 +1940,13 @@
     <t xml:space="preserve">OLHOSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Stainless Hood for DD Gas Kilns Product option do not apply</t>
+    <t xml:space="preserve">Olympic Stainless Hood for DD Gas Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">OLWINDOW24</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add 2" x 4" Rectangle Quartz Window Product option do not app</t>
+    <t xml:space="preserve">Olympic: ADD 2" x 4" Rectangle Quartz Window</t>
   </si>
   <si>
     <t xml:space="preserve">127.00</t>
@@ -1937,7 +1958,7 @@
     <t xml:space="preserve">OLWINDOW2R</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add 2" Round Quartz Window Product option do not apply</t>
+    <t xml:space="preserve">Olympic: ADD 2" Round Quartz Window</t>
   </si>
   <si>
     <t xml:space="preserve">94.00</t>
@@ -1949,7 +1970,7 @@
     <t xml:space="preserve">OLHB64E</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Hotbox or HB64 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic Hotbox or HB64 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">63.75</t>
@@ -1958,7 +1979,7 @@
     <t xml:space="preserve">OLO20FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add the Oval 20 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">ADD the Oval 20 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">371.25</t>
@@ -1973,7 +1994,7 @@
     <t xml:space="preserve">OLDM1823FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 1818 and 1823 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 1818 and 1823 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">228.75</t>
@@ -1985,7 +2006,7 @@
     <t xml:space="preserve">OLDM182327FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 2318, 2323 and 2327 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 2318, 2323 and 2327 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">427.50</t>
@@ -1997,7 +2018,7 @@
     <t xml:space="preserve">OLDM2818FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 2818 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 2818 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: Dual Media Kilns — 28H"</t>
@@ -2006,13 +2027,13 @@
     <t xml:space="preserve">OLDM2327FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 2823 and 2827 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 2823 and 2827 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">OLDM2523FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 2523 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 2523 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">772.50</t>
@@ -2024,7 +2045,7 @@
     <t xml:space="preserve">OLDM301823FK</t>
   </si>
   <si>
-    <t xml:space="preserve">DM 3018 and 3023 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">DM 3018 and 3023 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">903.75</t>
@@ -2036,7 +2057,7 @@
     <t xml:space="preserve">OL2731GFK</t>
   </si>
   <si>
-    <t xml:space="preserve">2327, 2331 Torchbearer Furniture Kit Product option do not apply Furni</t>
+    <t xml:space="preserve">2327, 2331 TorcHBearer Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">567.00</t>
@@ -2048,7 +2069,7 @@
     <t xml:space="preserve">OLGF2ETLCSK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic GF2ETLC : Add the shelf kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic GF2ETLC : ADD the shelf kit</t>
   </si>
   <si>
     <t xml:space="preserve">250.00</t>
@@ -2060,7 +2081,7 @@
     <t xml:space="preserve">OLGF3ETLCSK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add Shelf kit to GF3ETLC Save 20% Product option do not apply</t>
+    <t xml:space="preserve">Olympi: ADD Shelf kit to GF3ETLC Save 20%</t>
   </si>
   <si>
     <t xml:space="preserve">330.00</t>
@@ -2072,7 +2093,7 @@
     <t xml:space="preserve">OLEK3Z</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 3 Zone Option for Electric Kilns Product option do not apply</t>
+    <t xml:space="preserve">Olympic 3 Zone Option for Electric Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">240.00</t>
@@ -2087,7 +2108,7 @@
     <t xml:space="preserve">OL18BR</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Blank ring to 18" (non "H") Adds 0.66 cu ft. Product option do not</t>
+    <t xml:space="preserve">ADD Blank ring to 18" (non "H") ADDs 0.66 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: 18" Blank Ring</t>
@@ -2096,7 +2117,7 @@
     <t xml:space="preserve">OL18BRH</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Blank ring to 18" "H" Models Adds 0.66 cu ft. Product option do no</t>
+    <t xml:space="preserve">ADD Blank ring to 18" "H" Models ADDs 0.66 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: 18H" Blank Ring</t>
@@ -2105,7 +2126,7 @@
     <t xml:space="preserve">OL23HFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Furniture Kit to 23"H Standard Electric Kiln Product option do not</t>
+    <t xml:space="preserve">ADD Furniture Kit to 23"H Standard Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">491.25</t>
@@ -2117,7 +2138,7 @@
     <t xml:space="preserve">OL18HFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Furniture Kit to Standard 18" Electric Kiln Product option do not </t>
+    <t xml:space="preserve">ADD Furniture Kit to Standard 18" Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">257.00</t>
@@ -2132,7 +2153,7 @@
     <t xml:space="preserve">OL28HFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Furniture Kit to 28"H Standard Electric Kiln Product option do not</t>
+    <t xml:space="preserve">ADD Furniture Kit to 28"H Standard Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: 28" Wide Stackable Kilns — 28H"</t>
@@ -2141,7 +2162,7 @@
     <t xml:space="preserve">OL28FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Furniture Kit to 28" Standard Electric Kiln Product option do not </t>
+    <t xml:space="preserve">ADD Furniture Kit to 28" Standard Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">495.00</t>
@@ -2153,7 +2174,7 @@
     <t xml:space="preserve">OL23FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Furniture Kit to 23" Electric Kiln</t>
+    <t xml:space="preserve">ADD Furniture Kit to 23" 2.5" Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: 23" Wide Stackable Kilns — 23"</t>
@@ -2162,7 +2183,7 @@
     <t xml:space="preserve">OL23BR</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Blank ring to 23" (non "H") Adds 1.05 cu ft. Product option do not</t>
+    <t xml:space="preserve">ADD Blank ring to 23" (non "H") ADDs 1.05 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: 23" Blank Ring</t>
@@ -2171,7 +2192,7 @@
     <t xml:space="preserve">OL23HBR</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Blank ring to 23" ("H" Models) Adds 1.05 cu ft. Product option do </t>
+    <t xml:space="preserve">ADD Blank ring to 23" ("H" Models) ADDs 1.05 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: 23H" Blank Ring</t>
@@ -2180,7 +2201,7 @@
     <t xml:space="preserve">OL28HBR</t>
   </si>
   <si>
-    <t xml:space="preserve">Add Blank ring to 28" ("H" and Non-"H" Models) Adds 1.67 cu ft. Produc</t>
+    <t xml:space="preserve">ADD Blank ring to 28" ("H" and Non-"H"Models) ADDs 1.67 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">385.00</t>
@@ -2192,7 +2213,7 @@
     <t xml:space="preserve">OLDTFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Doll/Test Mini Oval Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic Doll/Test Mini Oval Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">71.25</t>
@@ -2204,7 +2225,7 @@
     <t xml:space="preserve">OLHB8FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic HB84, HB86 and HB89 Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic HB84, HB86 and HB89 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">67.50</t>
@@ -2216,7 +2237,7 @@
     <t xml:space="preserve">OL12FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 129 and 1214-120 Furniture Kit Product option do not apply Fur</t>
+    <t xml:space="preserve">Olympic 129 and 1214-120 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">122.25</t>
@@ -2228,7 +2249,7 @@
     <t xml:space="preserve">OLVMEK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Vent Master Expansion Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic: Vent Master Expansion Kit</t>
   </si>
   <si>
     <t xml:space="preserve">180.00</t>
@@ -2240,7 +2261,7 @@
     <t xml:space="preserve">OLDM3P</t>
   </si>
   <si>
-    <t xml:space="preserve">Three Phase Product option do not apply</t>
+    <t xml:space="preserve">Three Phase</t>
   </si>
   <si>
     <t xml:space="preserve">90.00</t>
@@ -2255,7 +2276,7 @@
     <t xml:space="preserve">OLCEK3Z</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Zone Control Option for Commercial Electric Kilns Product opti</t>
+    <t xml:space="preserve">Olympic Zone Control Option for Commercial Electric Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">listing says "zone control" without a count; 2-zone is $150</t>
@@ -2264,7 +2285,7 @@
     <t xml:space="preserve">OLKSC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kiln Star Controller Product option do not apply</t>
+    <t xml:space="preserve">Olympic Kiln Star Controller</t>
   </si>
   <si>
     <t xml:space="preserve">50.00</t>
@@ -2276,7 +2297,7 @@
     <t xml:space="preserve">OL2827GFK</t>
   </si>
   <si>
-    <t xml:space="preserve">2827 and 2831 Torchbearer Furniture Kit Product option do not apply Fu</t>
+    <t xml:space="preserve">2827 and 2831 TorcHBearer Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">622.50</t>
@@ -2288,7 +2309,7 @@
     <t xml:space="preserve">OLEKC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Castors Product option do not apply</t>
+    <t xml:space="preserve">Olympic Castors</t>
   </si>
   <si>
     <t xml:space="preserve">265.00</t>
@@ -2303,7 +2324,7 @@
     <t xml:space="preserve">OLMAS28SFK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic MAS28 Series Furniture Kit Product option do not apply</t>
+    <t xml:space="preserve">Olympic MAS28 Series Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: Medallion Artist Series — 28H"</t>
@@ -2315,7 +2336,7 @@
     <t xml:space="preserve">OLGENESIS</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns Upgrade to Genesis Touchscreen Controller Product option</t>
+    <t xml:space="preserve">Olympic Kilns Upgrade to Genesis Touchscreen Controller</t>
   </si>
   <si>
     <t xml:space="preserve">110.00</t>
@@ -2330,13 +2351,13 @@
     <t xml:space="preserve">OLSC12K</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 120V 12 Key Kiln Star Controller Product option do not apply</t>
+    <t xml:space="preserve">Olympic 120V 12 Key Kiln Star Controller</t>
   </si>
   <si>
     <t xml:space="preserve">OLVG3DC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Vitrigraph: Upgrade to 3 Key Digital Controller Product option</t>
+    <t xml:space="preserve">Olympic Vitrigraph: Upgrade to 3 Key Digital Controller</t>
   </si>
   <si>
     <t xml:space="preserve">170.00</t>
@@ -2348,7 +2369,7 @@
     <t xml:space="preserve">OES12KC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Electro-Sitter : Kiln Star 12 Key Controller Product option do</t>
+    <t xml:space="preserve">Olympic Electro-Sitter : Kiln Star 12 Key Controller</t>
   </si>
   <si>
     <t xml:space="preserve">Electro Sitter KilnStar is the base version; no separate upgrade price in the list</t>
@@ -2357,7 +2378,7 @@
     <t xml:space="preserve">OESGENESISTSC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Electro-Sitter : Genesis Touch-Screen Controller Product optio</t>
+    <t xml:space="preserve">Olympic Electro-Sitter : Genesis Touch-Screen Controller</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: Electro Sitter Genesis $1,450 less KilnStar $1,250</t>
@@ -2369,7 +2390,7 @@
     <t xml:space="preserve">OLLSS</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add Lid Safety Shut Off Product option do not apply</t>
+    <t xml:space="preserve">Olympic: ADD Lid Safety Shut Off</t>
   </si>
   <si>
     <t xml:space="preserve">95.00</t>
@@ -2381,7 +2402,7 @@
     <t xml:space="preserve">OLDME</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add Lid Elements for Glass and Ceramics: ADDS 8 AMPS to the k</t>
+    <t xml:space="preserve">Olympic: ADD Lid Elements for Glass and Ceramics: ADDS 8 AMPS to the k</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: Dual Media (DM) Lid Element</t>
@@ -2390,7 +2411,7 @@
     <t xml:space="preserve">OLLA</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Add Lid Lift Assist PRoduct option do not apply</t>
+    <t xml:space="preserve">Olympic ADD Lid Lift Assist</t>
   </si>
   <si>
     <t xml:space="preserve">445.00</t>
@@ -2405,7 +2426,7 @@
     <t xml:space="preserve">OLL23PR</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Add Low Pressure Regulator for 23" or 28" Gas Kiln Product op</t>
+    <t xml:space="preserve">Olympic: Add Low Pressure Regulator for 23" or 28" Gas Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">Accessories: Low Pressure Regulator 23" &amp; 28"</t>
@@ -2414,7 +2435,7 @@
     <t xml:space="preserve">OLTL5432FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympi Kilns: Add Furniture Kit to TL5432 Product option do not apply</t>
+    <t xml:space="preserve">Olympi Kilns: ADD Furniture Kit to TL5432</t>
   </si>
   <si>
     <t xml:space="preserve">2478.75</t>
@@ -2426,19 +2447,19 @@
     <t xml:space="preserve">OLPHASE3</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 3 Phase Option Product option do not apply</t>
+    <t xml:space="preserve">Olympic 3 Phase Option</t>
   </si>
   <si>
     <t xml:space="preserve">OLLSO</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Auto Lid Shut-Off (Required in Europe) Product option do not </t>
+    <t xml:space="preserve">Olympic: Auto Lid Shut-Off (Required in Europe)</t>
   </si>
   <si>
     <t xml:space="preserve">OLVSSEK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic : Add Vent System to Standard Electric Kiln Product option do </t>
+    <t xml:space="preserve">Olympic : ADD Vent System to Standard Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">529.00</t>
@@ -2450,7 +2471,7 @@
     <t xml:space="preserve">OL20BR</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Add a 4.5" blank ring: Adds 1.3 cu ft. Product option do not a</t>
+    <t xml:space="preserve">Olympic ADD a 4.5" blank ring: ADDs 1.3 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">360.00</t>
@@ -2459,13 +2480,13 @@
     <t xml:space="preserve">OL30BR</t>
   </si>
   <si>
-    <t xml:space="preserve">Add a 4.5" blank ring: Adds 2.75 cu ft. Product option do not apply</t>
+    <t xml:space="preserve">ADD a 4.5" blank ring: ADDs 2.75 cu ft.</t>
   </si>
   <si>
     <t xml:space="preserve">OLCWLS</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Counter Weight Lid System Product option: Cannot Be Purchased</t>
+    <t xml:space="preserve">Olympic: Counter Weight Lid System: OPTION ONLY:</t>
   </si>
   <si>
     <t xml:space="preserve">"counter weight lid system" priced as Lid Assist; retro-fit is $750</t>
@@ -2474,7 +2495,7 @@
     <t xml:space="preserve">OLDVC</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic: Downdraft Venting System Product option do not apply</t>
+    <t xml:space="preserve">Olympic: Downdraft Venting System</t>
   </si>
   <si>
     <t xml:space="preserve">785.00</t>
@@ -2483,13 +2504,13 @@
     <t xml:space="preserve">OL3ZONE</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Stackable Add 3 Zone Option Product option do not apply</t>
+    <t xml:space="preserve">Olympic Stackable ADD 3 Zone Option</t>
   </si>
   <si>
     <t xml:space="preserve">OL3PCK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 3 Phase: Commercial Kilns Product option do not apply</t>
+    <t xml:space="preserve">Olympic 3 Phase: Commercial Kilns</t>
   </si>
   <si>
     <t xml:space="preserve">440.00</t>
@@ -2501,7 +2522,7 @@
     <t xml:space="preserve">OLSSR17</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns Solid State Relays for Commercial kilns FL17 and larger:</t>
+    <t xml:space="preserve">Olympic Solid State Relays for FL17, FL20,FL24</t>
   </si>
   <si>
     <t xml:space="preserve">600.00</t>
@@ -2510,13 +2531,13 @@
     <t xml:space="preserve">Solid State Relays: 76-100 Amps, 1 phase</t>
   </si>
   <si>
-    <t xml:space="preserve">relays are priced by amperage; FL17 draws 70/81A so the 76-100A band is used</t>
+    <t xml:space="preserve">relays are priced by amperage; FL17/FL20/FL24 all draw 70-98A, so the 76-100A band applies</t>
   </si>
   <si>
     <t xml:space="preserve">OLSSR173P</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic Kilns Solid State Relays for Commercial kilns FL17 and larger </t>
+    <t xml:space="preserve">Olympic Solid State Relays for FL17, FL20,FL24 when 3 Phase</t>
   </si>
   <si>
     <t xml:space="preserve">850.00</t>
@@ -2528,7 +2549,7 @@
     <t xml:space="preserve">OLFL20FK</t>
   </si>
   <si>
-    <t xml:space="preserve">FURNITURE KIT FOR Olympic FL17 and FL20: 8 each – 13” x 26” x 1″ recta</t>
+    <t xml:space="preserve">Olympic FL17 and FL20 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">984.30</t>
@@ -2540,7 +2561,7 @@
     <t xml:space="preserve">OLPHASE3C</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic 3 Phase Option on large FL kilns Product option do not apply</t>
+    <t xml:space="preserve">Olympic 3 Phase Commercial Kilns Option</t>
   </si>
   <si>
     <t xml:space="preserve">OL480V</t>
@@ -2555,7 +2576,7 @@
     <t xml:space="preserve">OLFL45FK</t>
   </si>
   <si>
-    <t xml:space="preserve">FURNITURE KIT FOR Olympic FL4.5 4 ea. – 16” x 16” x 1” square shelves;</t>
+    <t xml:space="preserve">Olympic FL4.5 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">447.95</t>
@@ -2567,7 +2588,7 @@
     <t xml:space="preserve">OLFL55FK</t>
   </si>
   <si>
-    <t xml:space="preserve">FURNITURE KIT FOR Olympic FL5.5 4 ea. – 18” x 18” x 1” square shelves;</t>
+    <t xml:space="preserve">Olympic FL5.5 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: Large Capacity Kilns — FL5.5E</t>
@@ -2576,7 +2597,7 @@
     <t xml:space="preserve">OLFL8FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL8, FL10, FL12 Furniture Kit 8 ea. – 11” x 22” x 1” rectangle</t>
+    <t xml:space="preserve">Olympic FL8, FL10, FL12 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">799.00</t>
@@ -2588,7 +2609,7 @@
     <t xml:space="preserve">OLFL24FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL24 Furniture Kit 16 ea. – 16” x 16” x 1” square shelves; 16 </t>
+    <t xml:space="preserve">Olympic FL24 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1819.00</t>
@@ -2600,7 +2621,7 @@
     <t xml:space="preserve">OLFL27FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL27 and FL31 Furniture Kit 16 ea. –17” x 17” x 1” square shel</t>
+    <t xml:space="preserve">Olympic FL27, FL31 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: Large Capacity Kilns — FL27E, FL31E</t>
@@ -2609,7 +2630,7 @@
     <t xml:space="preserve">OLFL36FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL36 Furniture Kit 16 ea. – 18” x 18” x 1” square shelves; 16 </t>
+    <t xml:space="preserve">Olympic FL36 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">1889.00</t>
@@ -2621,7 +2642,7 @@
     <t xml:space="preserve">OLFL42FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL42 Furniture Kit 24 ea. – 11” x 22” x 1” rectangle shelves; </t>
+    <t xml:space="preserve">Olympic FL42 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">Furniture Kits: Large Capacity Kilns — FL42E</t>
@@ -2630,7 +2651,7 @@
     <t xml:space="preserve">OLFL53FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL53 Furniture Kit 32 ea. – 11” x 22” x 1” rectangle shelves; </t>
+    <t xml:space="preserve">Olympic FL53 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">3599.00</t>
@@ -2642,7 +2663,7 @@
     <t xml:space="preserve">OLFL64FK</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL64 Furniture Kit 16 ea. – 23” x 23” square shelves; 16 each </t>
+    <t xml:space="preserve">Olympic FL64 Furniture Kit</t>
   </si>
   <si>
     <t xml:space="preserve">2189.00</t>
@@ -2654,7 +2675,7 @@
     <t xml:space="preserve">OLFL10</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL-10 Front Loading Electric Kiln The Olympic FL-10 is a front</t>
+    <t xml:space="preserve">Olympic FL-10 Front Loading Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">8999.00</t>
@@ -2666,7 +2687,7 @@
     <t xml:space="preserve">OLFL45</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL-4.5 Front Loading Electric Kiln The Olympic FL-4.5 is a com</t>
+    <t xml:space="preserve">Olympic FL-4.5 Front Loading Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">6299.00</t>
@@ -2678,13 +2699,19 @@
     <t xml:space="preserve">OLFL24-old</t>
   </si>
   <si>
+    <t xml:space="preserve">Olympic FL-24 - ARCHIVE</t>
+  </si>
+  <si>
     <t xml:space="preserve">14599.00</t>
   </si>
   <si>
+    <t xml:space="preserve">listing is marked ARCHIVE — priced the same as the current FL24 listing</t>
+  </si>
+  <si>
     <t xml:space="preserve">OLFL36</t>
   </si>
   <si>
-    <t xml:space="preserve">Olympic FL-36 Front Loading Electric Kiln The Olympic FL-36 is Olympic</t>
+    <t xml:space="preserve">Olympic FL-36 Front Loading Electric Kiln</t>
   </si>
   <si>
     <t xml:space="preserve">21999.00</t>
@@ -3637,7 +3664,7 @@
         <v>0.136950904392765</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>84</v>
       </c>
@@ -3943,7 +3970,7 @@
         <v>0.109427609427609</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>128</v>
       </c>
@@ -4361,7 +4388,7 @@
         <v>0.120229007633588</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>188</v>
       </c>
@@ -4417,7 +4444,7 @@
         <v>0.103507271171942</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>196</v>
       </c>
@@ -4605,7 +4632,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>224</v>
       </c>
@@ -4662,17 +4689,17 @@
         <v>232</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4" t="n">
         <v>30975</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>13</v>
@@ -4683,22 +4710,22 @@
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4" t="n">
         <v>11800</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>13</v>
@@ -4711,26 +4738,26 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8" t="n">
         <v>1425</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I58" s="9" t="str">
         <f aca="false">IF(OR(E58="",D58=""),"",E58/D58-1)</f>
@@ -4739,20 +4766,20 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4" t="n">
         <v>300</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>13</v>
@@ -4764,49 +4791,49 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B60" s="7" t="s">
+      <c r="A60" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8" t="n">
+      <c r="C60" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4" t="n">
         <v>1600</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="7" t="s">
+      <c r="F60" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I60" s="9" t="str">
+      <c r="G60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I60" s="5" t="str">
         <f aca="false">IF(OR(E60="",D60=""),"",E60/D60-1)</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4" t="n">
         <v>1700</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>13</v>
@@ -4819,20 +4846,20 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4" t="n">
         <v>1800</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>13</v>
@@ -4845,13 +4872,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>3190</v>
@@ -4860,7 +4887,7 @@
         <v>3510</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>13</v>
@@ -4873,13 +4900,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>3660</v>
@@ -4888,7 +4915,7 @@
         <v>3925</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>13</v>
@@ -4901,13 +4928,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>4205</v>
@@ -4916,7 +4943,7 @@
         <v>4625</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>13</v>
@@ -4929,13 +4956,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>4710</v>
@@ -4944,7 +4971,7 @@
         <v>5185</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>13</v>
@@ -4957,13 +4984,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>5025</v>
@@ -4972,7 +4999,7 @@
         <v>5530</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>13</v>
@@ -4985,13 +5012,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>6180</v>
@@ -5000,7 +5027,7 @@
         <v>6800</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>13</v>
@@ -5013,13 +5040,13 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>4950</v>
@@ -5028,7 +5055,7 @@
         <v>5450</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>13</v>
@@ -5041,13 +5068,13 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>5440</v>
@@ -5056,7 +5083,7 @@
         <v>5985</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>13</v>
@@ -5069,13 +5096,13 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D71" s="4" t="n">
         <v>5835</v>
@@ -5084,7 +5111,7 @@
         <v>6425</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>13</v>
@@ -5097,13 +5124,13 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>6820</v>
@@ -5112,7 +5139,7 @@
         <v>7505</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>13</v>
@@ -5125,13 +5152,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D73" s="4" t="n">
         <v>7310</v>
@@ -5140,7 +5167,7 @@
         <v>8050</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>13</v>
@@ -5153,10 +5180,10 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>36</v>
@@ -5179,13 +5206,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>3190</v>
@@ -5194,7 +5221,7 @@
         <v>3510</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>13</v>
@@ -5205,12 +5232,12 @@
         <v>0.100313479623825</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>150</v>
@@ -5222,7 +5249,7 @@
         <v>5000</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>13</v>
@@ -5235,13 +5262,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>5325</v>
@@ -5250,7 +5277,7 @@
         <v>5860</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>13</v>
@@ -5261,15 +5288,15 @@
         <v>0.100469483568075</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D78" s="4" t="n">
         <v>6320</v>
@@ -5278,7 +5305,7 @@
         <v>6950</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>13</v>
@@ -5291,13 +5318,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D79" s="4" t="n">
         <v>7510</v>
@@ -5306,7 +5333,7 @@
         <v>8275</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>13</v>
@@ -5319,13 +5346,13 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D80" s="4" t="n">
         <v>6680</v>
@@ -5334,7 +5361,7 @@
         <v>7350</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>13</v>
@@ -5347,13 +5374,13 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D81" s="4" t="n">
         <v>7230</v>
@@ -5362,7 +5389,7 @@
         <v>7950</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>13</v>
@@ -5373,15 +5400,15 @@
         <v>0.099585062240664</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D82" s="4" t="n">
         <v>10260</v>
@@ -5390,7 +5417,7 @@
         <v>11300</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>13</v>
@@ -5401,15 +5428,15 @@
         <v>0.101364522417154</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>12410</v>
@@ -5418,7 +5445,7 @@
         <v>13675</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>13</v>
@@ -5429,15 +5456,15 @@
         <v>0.101933924254633</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D84" s="4" t="n">
         <v>14190</v>
@@ -5446,7 +5473,7 @@
         <v>15625</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>13</v>
@@ -5459,13 +5486,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>16635</v>
@@ -5474,7 +5501,7 @@
         <v>18300</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>13</v>
@@ -5485,15 +5512,15 @@
         <v>0.100090171325518</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D86" s="4" t="n">
         <v>18570</v>
@@ -5502,7 +5529,7 @@
         <v>20500</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>13</v>
@@ -5513,15 +5540,15 @@
         <v>0.103931071620894</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D87" s="4" t="n">
         <v>21335</v>
@@ -5530,7 +5557,7 @@
         <v>23500</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>13</v>
@@ -5541,15 +5568,15 @@
         <v>0.101476447152566</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D88" s="4" t="n">
         <v>29960</v>
@@ -5558,7 +5585,7 @@
         <v>33000</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>13</v>
@@ -5569,15 +5596,15 @@
         <v>0.101468624833111</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D89" s="4" t="n">
         <v>8030</v>
@@ -5586,28 +5613,28 @@
         <v>8550</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="I89" s="5" t="n">
         <f aca="false">IF(OR(E89="",D89=""),"",E89/D89-1)</f>
         <v>0.0647571606475716</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D90" s="4" t="n">
         <v>8845</v>
@@ -5616,7 +5643,7 @@
         <v>9775</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>13</v>
@@ -5629,13 +5656,13 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D91" s="4" t="n">
         <v>3500</v>
@@ -5644,13 +5671,13 @@
         <v>3950</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="I91" s="5" t="n">
         <f aca="false">IF(OR(E91="",D91=""),"",E91/D91-1)</f>
@@ -5659,13 +5686,13 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>3860</v>
@@ -5674,7 +5701,7 @@
         <v>4250</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>13</v>
@@ -5687,13 +5714,13 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>1240</v>
@@ -5702,7 +5729,7 @@
         <v>1365</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>13</v>
@@ -5715,13 +5742,13 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>1120</v>
@@ -5730,7 +5757,7 @@
         <v>1235</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>13</v>
@@ -5743,13 +5770,13 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D95" s="4" t="n">
         <v>1285</v>
@@ -5758,7 +5785,7 @@
         <v>1525</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>13</v>
@@ -5771,13 +5798,13 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D96" s="4" t="n">
         <v>1315</v>
@@ -5786,7 +5813,7 @@
         <v>1450</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>13</v>
@@ -5799,13 +5826,13 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D97" s="4" t="n">
         <v>1620</v>
@@ -5814,7 +5841,7 @@
         <v>1700</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>13</v>
@@ -5827,13 +5854,13 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D98" s="4" t="n">
         <v>1460</v>
@@ -5842,7 +5869,7 @@
         <v>1600</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>13</v>
@@ -5855,20 +5882,20 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4" t="n">
         <v>100</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>13</v>
@@ -5881,26 +5908,26 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4" t="n">
         <v>1600</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="I100" s="5" t="str">
         <f aca="false">IF(OR(E100="",D100=""),"",E100/D100-1)</f>
@@ -5909,13 +5936,13 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>2465</v>
@@ -5924,7 +5951,7 @@
         <v>2725</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>13</v>
@@ -5937,13 +5964,13 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>2600</v>
@@ -5952,7 +5979,7 @@
         <v>2850</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>13</v>
@@ -5965,10 +5992,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>106</v>
@@ -5980,7 +6007,7 @@
         <v>3925</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>13</v>
@@ -5993,13 +6020,13 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>4035</v>
@@ -6008,7 +6035,7 @@
         <v>4450</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>13</v>
@@ -6021,13 +6048,13 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D105" s="4" t="n">
         <v>4495</v>
@@ -6036,13 +6063,13 @@
         <v>4950</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="I105" s="5" t="n">
         <f aca="false">IF(OR(E105="",D105=""),"",E105/D105-1)</f>
@@ -6051,13 +6078,13 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D106" s="4" t="n">
         <v>4790</v>
@@ -6066,7 +6093,7 @@
         <v>5300</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>13</v>
@@ -6079,13 +6106,13 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="D107" s="4" t="n">
         <v>4380</v>
@@ -6094,7 +6121,7 @@
         <v>4825</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>13</v>
@@ -6107,13 +6134,13 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="D108" s="4" t="n">
         <v>5330</v>
@@ -6122,13 +6149,13 @@
         <v>5270</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="I108" s="5" t="n">
         <f aca="false">IF(OR(E108="",D108=""),"",E108/D108-1)</f>
@@ -6137,13 +6164,13 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>4845</v>
@@ -6152,7 +6179,7 @@
         <v>5875</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>13</v>
@@ -6165,13 +6192,13 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D110" s="4" t="n">
         <v>5035</v>
@@ -6180,7 +6207,7 @@
         <v>5550</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>13</v>
@@ -6193,13 +6220,13 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="D111" s="4" t="n">
         <v>5710</v>
@@ -6208,7 +6235,7 @@
         <v>6300</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>13</v>
@@ -6221,13 +6248,13 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D112" s="4" t="n">
         <v>6300</v>
@@ -6236,7 +6263,7 @@
         <v>6950</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>13</v>
@@ -6249,13 +6276,13 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D113" s="4" t="n">
         <v>6920</v>
@@ -6264,7 +6291,7 @@
         <v>7625</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>13</v>
@@ -6277,13 +6304,13 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="D114" s="4" t="n">
         <v>6330</v>
@@ -6292,7 +6319,7 @@
         <v>7200</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>13</v>
@@ -6305,13 +6332,13 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D115" s="4" t="n">
         <v>6820</v>
@@ -6320,7 +6347,7 @@
         <v>7700</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>13</v>
@@ -6333,13 +6360,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D116" s="4" t="n">
         <v>7590</v>
@@ -6348,7 +6375,7 @@
         <v>8500</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>13</v>
@@ -6361,13 +6388,13 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>8220</v>
@@ -6376,7 +6403,7 @@
         <v>9050</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>13</v>
@@ -6389,13 +6416,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D118" s="4" t="n">
         <v>1555</v>
@@ -6404,7 +6431,7 @@
         <v>1710</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>13</v>
@@ -6417,20 +6444,20 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4" t="n">
         <v>15</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>13</v>
@@ -6443,13 +6470,13 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D120" s="4" t="n">
         <v>10330</v>
@@ -6458,7 +6485,7 @@
         <v>11500</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>13</v>
@@ -6471,13 +6498,13 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D121" s="4" t="n">
         <v>19835</v>
@@ -6486,13 +6513,13 @@
         <v>22000</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="I121" s="5" t="n">
         <f aca="false">IF(OR(E121="",D121=""),"",E121/D121-1)</f>
@@ -6501,13 +6528,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="D122" s="4" t="n">
         <v>1990</v>
@@ -6516,7 +6543,7 @@
         <v>2200</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>13</v>
@@ -6527,15 +6554,15 @@
         <v>0.105527638190955</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
@@ -6544,22 +6571,22 @@
         <v>18</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I123" s="9" t="str">
         <f aca="false">IF(OR(E123="",D123=""),"",E123/D123-1)</f>
         <v/>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
@@ -6568,22 +6595,22 @@
         <v>18</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I124" s="9" t="str">
         <f aca="false">IF(OR(E124="",D124=""),"",E124/D124-1)</f>
         <v/>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
@@ -6592,22 +6619,22 @@
         <v>18</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I125" s="9" t="str">
         <f aca="false">IF(OR(E125="",D125=""),"",E125/D125-1)</f>
         <v/>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
@@ -6616,22 +6643,22 @@
         <v>18</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I126" s="9" t="str">
         <f aca="false">IF(OR(E126="",D126=""),"",E126/D126-1)</f>
         <v/>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
@@ -6640,22 +6667,22 @@
         <v>18</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I127" s="9" t="str">
         <f aca="false">IF(OR(E127="",D127=""),"",E127/D127-1)</f>
         <v/>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
@@ -6664,22 +6691,22 @@
         <v>18</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I128" s="9" t="str">
         <f aca="false">IF(OR(E128="",D128=""),"",E128/D128-1)</f>
         <v/>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
@@ -6688,22 +6715,22 @@
         <v>18</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I129" s="9" t="str">
         <f aca="false">IF(OR(E129="",D129=""),"",E129/D129-1)</f>
         <v/>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
@@ -6712,22 +6739,22 @@
         <v>18</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="I130" s="9" t="str">
         <f aca="false">IF(OR(E130="",D130=""),"",E130/D130-1)</f>
         <v/>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="D131" s="4" t="n">
         <v>27190</v>
@@ -6736,7 +6763,7 @@
         <v>29950</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>13</v>
@@ -6749,20 +6776,20 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4" t="n">
         <v>650</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>24</v>
@@ -6775,20 +6802,20 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4" t="n">
         <v>1830</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>13</v>
@@ -6801,20 +6828,20 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4" t="n">
         <v>31</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>13</v>
@@ -6827,13 +6854,13 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="D135" s="8"/>
       <c r="E135" s="8" t="n">
@@ -6846,7 +6873,7 @@
         <v>38</v>
       </c>
       <c r="H135" s="7" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="I135" s="9" t="str">
         <f aca="false">IF(OR(E135="",D135=""),"",E135/D135-1)</f>
@@ -6855,20 +6882,20 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4" t="n">
         <v>505</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>13</v>
@@ -6881,20 +6908,20 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4" t="n">
         <v>935</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>13</v>
@@ -6907,20 +6934,20 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>13</v>
@@ -6933,20 +6960,20 @@
     </row>
     <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4" t="n">
         <v>380</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>13</v>
@@ -6959,20 +6986,20 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4" t="n">
         <v>285</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>13</v>
@@ -6985,20 +7012,20 @@
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4" t="n">
         <v>325</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>13</v>
@@ -7011,20 +7038,20 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="n">
         <v>1240</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>13</v>
@@ -7037,13 +7064,13 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D143" s="4" t="n">
         <v>1077</v>
@@ -7052,7 +7079,7 @@
         <v>1200</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>13</v>
@@ -7065,20 +7092,20 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4" t="n">
         <v>1240</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>13</v>
@@ -7091,10 +7118,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>36</v>
@@ -7110,7 +7137,7 @@
         <v>38</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="I145" s="9" t="str">
         <f aca="false">IF(OR(E145="",D145=""),"",E145/D145-1)</f>
@@ -7119,20 +7146,20 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4" t="n">
         <v>1140</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>13</v>
@@ -7145,20 +7172,20 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="4" t="n">
         <v>1395</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>13</v>
@@ -7171,20 +7198,20 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4" t="n">
         <v>1240</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>13</v>
@@ -7197,20 +7224,20 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="4" t="n">
         <v>2105</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>13</v>
@@ -7223,26 +7250,26 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4" t="n">
         <v>1600</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="I150" s="5" t="str">
         <f aca="false">IF(OR(E150="",D150=""),"",E150/D150-1)</f>
@@ -7251,20 +7278,20 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4" t="n">
         <v>2185</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>13</v>
@@ -7277,20 +7304,20 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4" t="n">
         <v>2265</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>13</v>
@@ -7303,20 +7330,20 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4" t="n">
         <v>2585</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>13</v>
@@ -7329,20 +7356,20 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4" t="n">
         <v>260</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>13</v>
@@ -7355,20 +7382,20 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4" t="n">
         <v>175</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>13</v>
@@ -7381,20 +7408,20 @@
     </row>
     <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4" t="n">
         <v>1700</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G156" s="2" t="s">
         <v>13</v>
@@ -7407,20 +7434,20 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4" t="n">
         <v>1700</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>13</v>
@@ -7433,20 +7460,20 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4" t="n">
         <v>1750</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>13</v>
@@ -7459,20 +7486,20 @@
     </row>
     <row r="159" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4" t="n">
         <v>1800</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G159" s="2" t="s">
         <v>13</v>
@@ -7485,20 +7512,20 @@
     </row>
     <row r="160" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4" t="n">
         <v>150</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>13</v>
@@ -7511,20 +7538,20 @@
     </row>
     <row r="161" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4" t="n">
         <v>115</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>13</v>
@@ -7537,20 +7564,20 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4" t="n">
         <v>100</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>13</v>
@@ -7563,26 +7590,26 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="D163" s="8"/>
       <c r="E163" s="8" t="n">
         <v>745</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="I163" s="9" t="str">
         <f aca="false">IF(OR(E163="",D163=""),"",E163/D163-1)</f>
@@ -7591,20 +7618,20 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4" t="n">
         <v>385</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>13</v>
@@ -7617,20 +7644,20 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="D165" s="4"/>
       <c r="E165" s="4" t="n">
         <v>630</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>13</v>
@@ -7643,10 +7670,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>51</v>
@@ -7656,7 +7683,7 @@
         <v>880</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>13</v>
@@ -7669,10 +7696,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>51</v>
@@ -7682,7 +7709,7 @@
         <v>880</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>13</v>
@@ -7695,20 +7722,20 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4" t="n">
         <v>1255</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>13</v>
@@ -7721,20 +7748,20 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4" t="n">
         <v>1475</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>13</v>
@@ -7747,20 +7774,20 @@
     </row>
     <row r="170" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4" t="n">
         <v>756</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>13</v>
@@ -7773,20 +7800,20 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4" t="n">
         <v>315</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>13</v>
@@ -7799,20 +7826,20 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4" t="n">
         <v>385</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>13</v>
@@ -7825,26 +7852,26 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4" t="n">
         <v>295</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="I173" s="5" t="str">
         <f aca="false">IF(OR(E173="",D173=""),"",E173/D173-1)</f>
@@ -7853,20 +7880,20 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4" t="n">
         <v>300</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>13</v>
@@ -7879,10 +7906,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>36</v>
@@ -7892,7 +7919,7 @@
         <v>350</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>13</v>
@@ -7905,20 +7932,20 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4" t="n">
         <v>630</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>13</v>
@@ -7931,13 +7958,13 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="D177" s="4" t="n">
         <v>343</v>
@@ -7946,13 +7973,13 @@
         <v>385</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="I177" s="5" t="n">
         <f aca="false">IF(OR(E177="",D177=""),"",E177/D177-1)</f>
@@ -7961,10 +7988,10 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>51</v>
@@ -7974,7 +8001,7 @@
         <v>880</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>13</v>
@@ -7987,20 +8014,20 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="4" t="n">
         <v>820</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>13</v>
@@ -8013,20 +8040,20 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4" t="n">
         <v>585</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>13</v>
@@ -8039,10 +8066,10 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>36</v>
@@ -8052,7 +8079,7 @@
         <v>350</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>13</v>
@@ -8065,20 +8092,20 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4" t="n">
         <v>405</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>13</v>
@@ -8091,20 +8118,20 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4" t="n">
         <v>475</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>13</v>
@@ -8117,20 +8144,20 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4" t="n">
         <v>115</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>13</v>
@@ -8143,20 +8170,20 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="4" t="n">
         <v>108</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>13</v>
@@ -8169,20 +8196,20 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4" t="n">
         <v>160</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>13</v>
@@ -8195,20 +8222,20 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4" t="n">
         <v>275</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>13</v>
@@ -8221,26 +8248,26 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4" t="n">
         <v>110</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="I188" s="5" t="str">
         <f aca="false">IF(OR(E188="",D188=""),"",E188/D188-1)</f>
@@ -8249,10 +8276,10 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>54</v>
@@ -8262,13 +8289,13 @@
         <v>295</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="I189" s="5" t="str">
         <f aca="false">IF(OR(E189="",D189=""),"",E189/D189-1)</f>
@@ -8277,13 +8304,13 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
@@ -8292,7 +8319,7 @@
         <v>18</v>
       </c>
       <c r="H190" s="7" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="I190" s="9" t="str">
         <f aca="false">IF(OR(E190="",D190=""),"",E190/D190-1)</f>
@@ -8301,20 +8328,20 @@
     </row>
     <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4" t="n">
         <v>830</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>13</v>
@@ -8327,26 +8354,26 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4" t="n">
         <v>325</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="I192" s="5" t="str">
         <f aca="false">IF(OR(E192="",D192=""),"",E192/D192-1)</f>
@@ -8355,10 +8382,10 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>51</v>
@@ -8368,13 +8395,13 @@
         <v>880</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="G193" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="I193" s="5" t="str">
         <f aca="false">IF(OR(E193="",D193=""),"",E193/D193-1)</f>
@@ -8383,26 +8410,26 @@
     </row>
     <row r="194" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="D194" s="8"/>
       <c r="E194" s="8" t="n">
         <v>150</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="G194" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H194" s="7" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="I194" s="9" t="str">
         <f aca="false">IF(OR(E194="",D194=""),"",E194/D194-1)</f>
@@ -8411,13 +8438,13 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
@@ -8426,7 +8453,7 @@
         <v>18</v>
       </c>
       <c r="H195" s="7" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="I195" s="9" t="str">
         <f aca="false">IF(OR(E195="",D195=""),"",E195/D195-1)</f>
@@ -8435,13 +8462,13 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
@@ -8450,7 +8477,7 @@
         <v>18</v>
       </c>
       <c r="H196" s="7" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="I196" s="9" t="str">
         <f aca="false">IF(OR(E196="",D196=""),"",E196/D196-1)</f>
@@ -8459,13 +8486,13 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
@@ -8474,7 +8501,7 @@
         <v>18</v>
       </c>
       <c r="H197" s="7" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="I197" s="9" t="str">
         <f aca="false">IF(OR(E197="",D197=""),"",E197/D197-1)</f>
@@ -8483,26 +8510,26 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="4" t="n">
         <v>200</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="I198" s="5" t="str">
         <f aca="false">IF(OR(E198="",D198=""),"",E198/D198-1)</f>
@@ -8511,20 +8538,20 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4" t="n">
         <v>115</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>13</v>
@@ -8537,20 +8564,20 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="4" t="n">
         <v>650</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>24</v>
@@ -8563,26 +8590,26 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="4" t="n">
         <v>550</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="I201" s="5" t="str">
         <f aca="false">IF(OR(E201="",D201=""),"",E201/D201-1)</f>
@@ -8591,20 +8618,20 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="4" t="n">
         <v>275</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>13</v>
@@ -8617,20 +8644,20 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="4" t="n">
         <v>3635</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>13</v>
@@ -8643,26 +8670,26 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="4" t="n">
         <v>110</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="I204" s="5" t="str">
         <f aca="false">IF(OR(E204="",D204=""),"",E204/D204-1)</f>
@@ -8671,20 +8698,20 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="4" t="n">
         <v>115</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>13</v>
@@ -8697,20 +8724,20 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="4" t="n">
         <v>775</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>13</v>
@@ -8723,13 +8750,13 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="4" t="n">
@@ -8751,10 +8778,10 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>28</v>
@@ -8777,26 +8804,26 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="6" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="D209" s="8"/>
       <c r="E209" s="8" t="n">
         <v>550</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="G209" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H209" s="7" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="I209" s="9" t="str">
         <f aca="false">IF(OR(E209="",D209=""),"",E209/D209-1)</f>
@@ -8805,20 +8832,20 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="2" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="4" t="n">
         <v>775</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>13</v>
@@ -8831,26 +8858,26 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="4" t="n">
         <v>295</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="I211" s="5" t="str">
         <f aca="false">IF(OR(E211="",D211=""),"",E211/D211-1)</f>
@@ -8859,26 +8886,26 @@
     </row>
     <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="2" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4" t="n">
         <v>450</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="I212" s="5" t="str">
         <f aca="false">IF(OR(E212="",D212=""),"",E212/D212-1)</f>
@@ -8887,26 +8914,26 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="D213" s="8"/>
       <c r="E213" s="8" t="n">
         <v>650</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="G213" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H213" s="7" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="I213" s="9" t="str">
         <f aca="false">IF(OR(E213="",D213=""),"",E213/D213-1)</f>
@@ -8915,26 +8942,26 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="D214" s="8"/>
       <c r="E214" s="8" t="n">
         <v>925</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="G214" s="6" t="s">
         <v>38</v>
       </c>
       <c r="H214" s="7" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="I214" s="9" t="str">
         <f aca="false">IF(OR(E214="",D214=""),"",E214/D214-1)</f>
@@ -8943,13 +8970,13 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="D215" s="4" t="n">
         <v>1158</v>
@@ -8958,7 +8985,7 @@
         <v>1235</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>13</v>
@@ -8971,26 +8998,26 @@
     </row>
     <row r="216" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="4" t="n">
         <v>450</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>13</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="I216" s="5" t="str">
         <f aca="false">IF(OR(E216="",D216=""),"",E216/D216-1)</f>
@@ -8999,10 +9026,10 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>28</v>
@@ -9012,7 +9039,7 @@
         <v>550</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>13</v>
@@ -9025,13 +9052,13 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="D218" s="4" t="n">
         <v>527</v>
@@ -9040,7 +9067,7 @@
         <v>530</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>13</v>
@@ -9053,10 +9080,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>47</v>
@@ -9068,7 +9095,7 @@
         <v>545</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>13</v>
@@ -9081,13 +9108,13 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="D220" s="4" t="n">
         <v>942</v>
@@ -9096,7 +9123,7 @@
         <v>1195</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>13</v>
@@ -9109,13 +9136,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="D221" s="4" t="n">
         <v>2143</v>
@@ -9124,7 +9151,7 @@
         <v>2190</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>13</v>
@@ -9137,13 +9164,13 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="D222" s="4" t="n">
         <v>2143</v>
@@ -9152,7 +9179,7 @@
         <v>2270</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>13</v>
@@ -9165,13 +9192,13 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="D223" s="4" t="n">
         <v>2223</v>
@@ -9180,7 +9207,7 @@
         <v>2270</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>13</v>
@@ -9193,10 +9220,10 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>106</v>
@@ -9208,7 +9235,7 @@
         <v>3510</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>13</v>
@@ -9221,13 +9248,13 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="D225" s="4" t="n">
         <v>4256</v>
@@ -9236,7 +9263,7 @@
         <v>4680</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>13</v>
@@ -9249,13 +9276,13 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="D226" s="4" t="n">
         <v>2575</v>
@@ -9264,7 +9291,7 @@
         <v>2830</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>13</v>
@@ -9277,13 +9304,13 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="D227" s="4" t="n">
         <v>9755</v>
@@ -9292,7 +9319,7 @@
         <v>10750</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>13</v>
@@ -9305,13 +9332,13 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="D228" s="4" t="n">
         <v>6680</v>
@@ -9320,7 +9347,7 @@
         <v>7500</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>13</v>
@@ -9333,13 +9360,13 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>344</v>
+        <v>891</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D229" s="4" t="n">
         <v>16635</v>
@@ -9348,12 +9375,14 @@
         <v>18300</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H229" s="3"/>
+      <c r="H229" s="3" t="s">
+        <v>893</v>
+      </c>
       <c r="I229" s="5" t="n">
         <f aca="false">IF(OR(E229="",D229=""),"",E229/D229-1)</f>
         <v>0.100090171325518</v>
@@ -9361,13 +9390,13 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="D230" s="4" t="n">
         <v>24735</v>
@@ -9376,7 +9405,7 @@
         <v>27250</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>13</v>
@@ -9389,13 +9418,13 @@
     </row>
     <row r="231" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D231" s="4" t="n">
         <v>756</v>
@@ -9404,13 +9433,13 @@
         <v>935</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="G231" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="I231" s="5" t="n">
         <f aca="false">IF(OR(E231="",D231=""),"",E231/D231-1)</f>

--- a/olympic-new-compare-audit.xlsx
+++ b/olympic-new-compare-audit.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="902">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">Solid State Relays: 76-100 Amps, 1 phase</t>
   </si>
   <si>
-    <t xml:space="preserve">relays are priced by amperage; FL17/FL20/FL24 all draw 70-98A, so the 76-100A band applies</t>
+    <t xml:space="preserve">$650 confirmed by Sheffield Pottery — relays are priced by amperage and FL17/FL20/FL24 all draw 70-98A</t>
   </si>
   <si>
     <t xml:space="preserve">OLSSR173P</t>
@@ -2544,6 +2544,9 @@
   </si>
   <si>
     <t xml:space="preserve">Solid State Relays: 76-100 Amps, 3 phase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same 76-100A band as OLSSR17, which Sheffield confirmed at $650</t>
   </si>
   <si>
     <t xml:space="preserve">OLFL20FK</t>
@@ -8912,71 +8915,71 @@
         <v/>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="6" t="s">
+    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="C213" s="8" t="s">
+      <c r="C213" s="4" t="s">
         <v>833</v>
       </c>
-      <c r="D213" s="8"/>
-      <c r="E213" s="8" t="n">
+      <c r="D213" s="4"/>
+      <c r="E213" s="4" t="n">
         <v>650</v>
       </c>
-      <c r="F213" s="7" t="s">
+      <c r="F213" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="G213" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H213" s="7" t="s">
+      <c r="G213" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H213" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="I213" s="9" t="str">
+      <c r="I213" s="5" t="str">
         <f aca="false">IF(OR(E213="",D213=""),"",E213/D213-1)</f>
         <v/>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="C214" s="8" t="s">
+      <c r="C214" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="D214" s="8"/>
-      <c r="E214" s="8" t="n">
+      <c r="D214" s="4"/>
+      <c r="E214" s="4" t="n">
         <v>925</v>
       </c>
-      <c r="F214" s="7" t="s">
+      <c r="F214" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="G214" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H214" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="I214" s="9" t="str">
+      <c r="G214" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="I214" s="5" t="str">
         <f aca="false">IF(OR(E214="",D214=""),"",E214/D214-1)</f>
         <v/>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D215" s="4" t="n">
         <v>1158</v>
@@ -8985,7 +8988,7 @@
         <v>1235</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>13</v>
@@ -8998,10 +9001,10 @@
     </row>
     <row r="216" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="2" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>829</v>
@@ -9026,10 +9029,10 @@
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="2" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>28</v>
@@ -9039,7 +9042,7 @@
         <v>550</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>13</v>
@@ -9052,13 +9055,13 @@
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D218" s="4" t="n">
         <v>527</v>
@@ -9067,7 +9070,7 @@
         <v>530</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>13</v>
@@ -9080,10 +9083,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>47</v>
@@ -9095,7 +9098,7 @@
         <v>545</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>13</v>
@@ -9108,13 +9111,13 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D220" s="4" t="n">
         <v>942</v>
@@ -9123,7 +9126,7 @@
         <v>1195</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>13</v>
@@ -9136,13 +9139,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D221" s="4" t="n">
         <v>2143</v>
@@ -9151,7 +9154,7 @@
         <v>2190</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>13</v>
@@ -9164,13 +9167,13 @@
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D222" s="4" t="n">
         <v>2143</v>
@@ -9179,7 +9182,7 @@
         <v>2270</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>13</v>
@@ -9192,13 +9195,13 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="2" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D223" s="4" t="n">
         <v>2223</v>
@@ -9207,7 +9210,7 @@
         <v>2270</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>13</v>
@@ -9220,10 +9223,10 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>106</v>
@@ -9235,7 +9238,7 @@
         <v>3510</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>13</v>
@@ -9248,13 +9251,13 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D225" s="4" t="n">
         <v>4256</v>
@@ -9263,7 +9266,7 @@
         <v>4680</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>13</v>
@@ -9276,13 +9279,13 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D226" s="4" t="n">
         <v>2575</v>
@@ -9291,7 +9294,7 @@
         <v>2830</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>13</v>
@@ -9304,13 +9307,13 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D227" s="4" t="n">
         <v>9755</v>
@@ -9319,7 +9322,7 @@
         <v>10750</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G227" s="2" t="s">
         <v>13</v>
@@ -9332,13 +9335,13 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D228" s="4" t="n">
         <v>6680</v>
@@ -9347,7 +9350,7 @@
         <v>7500</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>13</v>
@@ -9360,13 +9363,13 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D229" s="4" t="n">
         <v>16635</v>
@@ -9381,7 +9384,7 @@
         <v>13</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="I229" s="5" t="n">
         <f aca="false">IF(OR(E229="",D229=""),"",E229/D229-1)</f>
@@ -9390,13 +9393,13 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D230" s="4" t="n">
         <v>24735</v>
@@ -9405,7 +9408,7 @@
         <v>27250</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>13</v>
@@ -9418,10 +9421,10 @@
     </row>
     <row r="231" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>678</v>
@@ -9439,7 +9442,7 @@
         <v>24</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="I231" s="5" t="n">
         <f aca="false">IF(OR(E231="",D231=""),"",E231/D231-1)</f>

--- a/olympic-new-compare-audit.xlsx
+++ b/olympic-new-compare-audit.xlsx
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">Olympic: ADD a 4.5" blank ring: ADDs 1.98 cu ft.</t>
   </si>
   <si>
-    <t xml:space="preserve">SKU says 2018 but "adds 1.98 cu ft" reads like a 25" oval ring</t>
+    <t xml:space="preserve">$480 confirmed by Sheffield Pottery (20" oval ring), despite the "1.98 cu ft" in the listing</t>
   </si>
   <si>
     <t xml:space="preserve">OL25HOFK</t>
@@ -7120,29 +7120,29 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D145" s="8"/>
-      <c r="E145" s="8" t="n">
+      <c r="D145" s="4"/>
+      <c r="E145" s="4" t="n">
         <v>480</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="F145" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G145" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H145" s="7" t="s">
+      <c r="G145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H145" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="I145" s="9" t="str">
+      <c r="I145" s="5" t="str">
         <f aca="false">IF(OR(E145="",D145=""),"",E145/D145-1)</f>
         <v/>
       </c>
